--- a/data/2026_06_05_sql_data_frame_creation_with_curated_subsets/subset_2/labeling.xlsx
+++ b/data/2026_06_05_sql_data_frame_creation_with_curated_subsets/subset_2/labeling.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar-my.sharepoint.com/personal/m_penuela_cgiar_org/Documents/Documents/projects/lmf/data/data_organization_june/subset_2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_F25DC773A252ABDACC10486279DD55085BDE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CE0DDF7-D66B-4BFB-9DE8-1596BC6BA3E8}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_F25DC773A252ABDACC10486279DD55085BDE58F2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7952475-3FA1-43A8-933C-F2C7021BFCD7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-8270" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="219">
   <si>
     <t>10_sample_serial_no</t>
   </si>
@@ -493,6 +493,195 @@
   </si>
   <si>
     <t>% NDF digestibility in 24 h</t>
+  </si>
+  <si>
+    <t>31_no</t>
+  </si>
+  <si>
+    <t>31_date</t>
+  </si>
+  <si>
+    <t>31_requisitioner</t>
+  </si>
+  <si>
+    <t>31_gene_bank_id</t>
+  </si>
+  <si>
+    <t>31_genus</t>
+  </si>
+  <si>
+    <t>31_species</t>
+  </si>
+  <si>
+    <t>31_tax_name</t>
+  </si>
+  <si>
+    <t>31_family</t>
+  </si>
+  <si>
+    <t>31_order</t>
+  </si>
+  <si>
+    <t>31_functional_group</t>
+  </si>
+  <si>
+    <t>31_ciat_id</t>
+  </si>
+  <si>
+    <t>31_set_ciat</t>
+  </si>
+  <si>
+    <t>31_batch</t>
+  </si>
+  <si>
+    <t>31_run</t>
+  </si>
+  <si>
+    <t>31_replication</t>
+  </si>
+  <si>
+    <t>31_syrange_no</t>
+  </si>
+  <si>
+    <t>31_sample_weight_g</t>
+  </si>
+  <si>
+    <t>31_dm_incubated_mg</t>
+  </si>
+  <si>
+    <t>31_digested_feed_mg</t>
+  </si>
+  <si>
+    <t>31_time_0h</t>
+  </si>
+  <si>
+    <t>31_gas_0h_ml</t>
+  </si>
+  <si>
+    <t>31_time_8h</t>
+  </si>
+  <si>
+    <t>31_gas_8h_ml</t>
+  </si>
+  <si>
+    <t>31_ch4_8h_percentage</t>
+  </si>
+  <si>
+    <t>31_v8_push_back_ml</t>
+  </si>
+  <si>
+    <t>31_time_24h</t>
+  </si>
+  <si>
+    <t>31_gas_24h_ml</t>
+  </si>
+  <si>
+    <t>31_ch4_24h_percentage</t>
+  </si>
+  <si>
+    <t>31_remarks_1</t>
+  </si>
+  <si>
+    <t>31_gp_8h_ml</t>
+  </si>
+  <si>
+    <t>31_gp_8_24h</t>
+  </si>
+  <si>
+    <t>31_net_gas_8h_ml</t>
+  </si>
+  <si>
+    <t>31_net_gas_8_24h_ml2</t>
+  </si>
+  <si>
+    <t>31_net_gas_24h_ml</t>
+  </si>
+  <si>
+    <t>31_ch4_8h_ml</t>
+  </si>
+  <si>
+    <t>31_ch4_8_24h_ml</t>
+  </si>
+  <si>
+    <t>31_ch4_24h_ml</t>
+  </si>
+  <si>
+    <t>31_gas_ml_g_dm_incubated_24h</t>
+  </si>
+  <si>
+    <t>31_percentage_dmd_truly_digestibility</t>
+  </si>
+  <si>
+    <t>31_part_fact</t>
+  </si>
+  <si>
+    <t>31_ch4_percentage_in_gas_8h</t>
+  </si>
+  <si>
+    <t>31_ch4_percentage_in_gas_24h</t>
+  </si>
+  <si>
+    <t>31_ch4_ml_g_dm_incubated_24h</t>
+  </si>
+  <si>
+    <t>31_ch4_ml_g_dmd_24h</t>
+  </si>
+  <si>
+    <t>31_ch4_ml_g_ndf_digested_in_24h</t>
+  </si>
+  <si>
+    <t>31_ch4_g_g_dm_incubated_24h</t>
+  </si>
+  <si>
+    <t>31_ch4_g_g_dmd_24h</t>
+  </si>
+  <si>
+    <t>Sample weight, g</t>
+  </si>
+  <si>
+    <t>DM Incubated, mg</t>
+  </si>
+  <si>
+    <t>Time 0h</t>
+  </si>
+  <si>
+    <t>Gas 0h, ml</t>
+  </si>
+  <si>
+    <t>Time 8h</t>
+  </si>
+  <si>
+    <t>Gas 8h, ml</t>
+  </si>
+  <si>
+    <t>V8 Push back, ml</t>
+  </si>
+  <si>
+    <t>Time 24h</t>
+  </si>
+  <si>
+    <t>Gas 24h, ml</t>
+  </si>
+  <si>
+    <t>GP 8h, ml</t>
+  </si>
+  <si>
+    <t>GP 8-24h, ml</t>
+  </si>
+  <si>
+    <t>Net gas 8-24h, ml2</t>
+  </si>
+  <si>
+    <t>CH4 8h, ml</t>
+  </si>
+  <si>
+    <t>CH4 8-24h, ml</t>
+  </si>
+  <si>
+    <t>CH4 24h, ml</t>
+  </si>
+  <si>
+    <t>32_no</t>
   </si>
 </sst>
 </file>
@@ -545,6 +734,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -810,15 +1003,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:AF19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:AU23"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -868,7 +1061,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -918,12 +1111,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -1021,7 +1214,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>64</v>
       </c>
@@ -1116,12 +1309,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>89</v>
       </c>
@@ -1192,7 +1385,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>64</v>
       </c>
@@ -1263,14 +1456,14 @@
         <v>122</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>123</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s">
         <v>124</v>
@@ -1348,7 +1541,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:47" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>64</v>
       </c>
@@ -1426,6 +1619,292 @@
       </c>
       <c r="Z19" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>156</v>
+      </c>
+      <c r="B22" t="s">
+        <v>157</v>
+      </c>
+      <c r="C22" t="s">
+        <v>158</v>
+      </c>
+      <c r="D22" t="s">
+        <v>159</v>
+      </c>
+      <c r="E22" t="s">
+        <v>160</v>
+      </c>
+      <c r="F22" t="s">
+        <v>161</v>
+      </c>
+      <c r="G22" t="s">
+        <v>162</v>
+      </c>
+      <c r="H22" t="s">
+        <v>163</v>
+      </c>
+      <c r="I22" t="s">
+        <v>164</v>
+      </c>
+      <c r="J22" t="s">
+        <v>165</v>
+      </c>
+      <c r="K22" t="s">
+        <v>166</v>
+      </c>
+      <c r="L22" t="s">
+        <v>167</v>
+      </c>
+      <c r="M22" t="s">
+        <v>168</v>
+      </c>
+      <c r="N22" t="s">
+        <v>169</v>
+      </c>
+      <c r="O22" t="s">
+        <v>170</v>
+      </c>
+      <c r="P22" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>172</v>
+      </c>
+      <c r="R22" t="s">
+        <v>173</v>
+      </c>
+      <c r="S22" t="s">
+        <v>174</v>
+      </c>
+      <c r="T22" t="s">
+        <v>175</v>
+      </c>
+      <c r="U22" t="s">
+        <v>176</v>
+      </c>
+      <c r="V22" t="s">
+        <v>177</v>
+      </c>
+      <c r="W22" t="s">
+        <v>178</v>
+      </c>
+      <c r="X22" t="s">
+        <v>179</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>181</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>182</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>183</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>184</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>185</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>186</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>187</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>188</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>189</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>190</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>191</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>192</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM22" t="s">
+        <v>194</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>195</v>
+      </c>
+      <c r="AO22" t="s">
+        <v>196</v>
+      </c>
+      <c r="AP22" t="s">
+        <v>197</v>
+      </c>
+      <c r="AQ22" t="s">
+        <v>198</v>
+      </c>
+      <c r="AR22" t="s">
+        <v>199</v>
+      </c>
+      <c r="AS22" t="s">
+        <v>200</v>
+      </c>
+      <c r="AT22" t="s">
+        <v>201</v>
+      </c>
+      <c r="AU22" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="23" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" t="s">
+        <v>24</v>
+      </c>
+      <c r="G23" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" t="s">
+        <v>26</v>
+      </c>
+      <c r="I23" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" t="s">
+        <v>28</v>
+      </c>
+      <c r="K23" t="s">
+        <v>67</v>
+      </c>
+      <c r="L23" t="s">
+        <v>20</v>
+      </c>
+      <c r="M23" t="s">
+        <v>68</v>
+      </c>
+      <c r="N23" t="s">
+        <v>69</v>
+      </c>
+      <c r="O23" t="s">
+        <v>70</v>
+      </c>
+      <c r="P23" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>203</v>
+      </c>
+      <c r="R23" t="s">
+        <v>204</v>
+      </c>
+      <c r="S23" t="s">
+        <v>152</v>
+      </c>
+      <c r="T23" t="s">
+        <v>205</v>
+      </c>
+      <c r="U23" t="s">
+        <v>206</v>
+      </c>
+      <c r="V23" t="s">
+        <v>207</v>
+      </c>
+      <c r="W23" t="s">
+        <v>208</v>
+      </c>
+      <c r="X23" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>210</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>211</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>212</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>213</v>
+      </c>
+      <c r="AF23" t="s">
+        <v>74</v>
+      </c>
+      <c r="AG23" t="s">
+        <v>214</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>75</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>215</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>216</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>217</v>
+      </c>
+      <c r="AL23" t="s">
+        <v>76</v>
+      </c>
+      <c r="AM23" t="s">
+        <v>77</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>78</v>
+      </c>
+      <c r="AO23" t="s">
+        <v>79</v>
+      </c>
+      <c r="AP23" t="s">
+        <v>80</v>
+      </c>
+      <c r="AQ23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AR23" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS23" t="s">
+        <v>83</v>
+      </c>
+      <c r="AT23" t="s">
+        <v>84</v>
+      </c>
+      <c r="AU23" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
